--- a/grupos/5AEM - Estadisticos 20221.xlsx
+++ b/grupos/5AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="143">
   <si>
     <t>Materia</t>
   </si>
@@ -185,6 +185,9 @@
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -194,9 +197,6 @@
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -212,211 +212,211 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>BERNABE</t>
   </si>
   <si>
+    <t>BUENO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ADELFO</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
     <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>DIEGO ADELFO</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
   </si>
   <si>
     <t>JESUS HAZAEL</t>
@@ -969,25 +969,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1011,25 +1011,25 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1058,25 +1058,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1100,16 +1100,16 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1147,25 +1147,25 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1189,25 +1189,25 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1236,25 +1236,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1278,16 +1278,16 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1296,7 +1296,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1325,25 +1325,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1367,16 +1367,16 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1414,25 +1414,25 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1456,7 +1456,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1465,16 +1465,16 @@
         <v>9</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1503,25 +1503,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1545,7 +1545,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1554,7 +1554,7 @@
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1563,7 +1563,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1592,25 +1592,25 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1640,7 +1640,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1649,10 +1649,10 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1681,25 +1681,25 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1723,13 +1723,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>7</v>
@@ -1738,10 +1738,10 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1770,25 +1770,25 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1812,7 +1812,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1821,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -1859,25 +1859,25 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1901,7 +1901,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1916,10 +1916,10 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1948,25 +1948,25 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -2005,10 +2005,10 @@
         <v>10</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2037,25 +2037,25 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2079,7 +2079,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2097,7 +2097,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2126,25 +2126,25 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2174,10 +2174,10 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>10</v>
@@ -2215,25 +2215,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2257,13 +2257,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>10</v>
@@ -2304,25 +2304,25 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2346,25 +2346,25 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2384,7 +2384,7 @@
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2393,25 +2393,25 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2441,19 +2441,19 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2482,25 +2482,25 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2524,7 +2524,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2536,7 +2536,7 @@
         <v>9</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2571,25 +2571,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2613,7 +2613,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2660,25 +2660,25 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2708,19 +2708,19 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2749,25 +2749,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2791,13 +2791,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>-1</v>
@@ -2806,10 +2806,10 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2838,25 +2838,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2886,10 +2886,10 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2927,25 +2927,25 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2975,10 +2975,10 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -3016,25 +3016,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3064,16 +3064,16 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -3105,25 +3105,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3150,13 +3150,13 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>10</v>
@@ -3165,7 +3165,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3194,25 +3194,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3239,10 +3239,10 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>5</v>
@@ -3254,7 +3254,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3283,25 +3283,25 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3325,13 +3325,13 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3372,25 +3372,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3414,16 +3414,16 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3432,7 +3432,7 @@
         <v>6</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3461,25 +3461,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3503,7 +3503,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3515,13 +3515,13 @@
         <v>-1</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3550,25 +3550,25 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3595,10 +3595,10 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z33">
         <v>9</v>
@@ -3607,7 +3607,7 @@
         <v>10</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC33">
         <v>10</v>
@@ -3639,25 +3639,25 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3681,16 +3681,16 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>10</v>
@@ -3699,7 +3699,7 @@
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3764,19 +3764,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>35.48</v>
+        <v>70.97</v>
       </c>
       <c r="G2">
-        <v>58.06</v>
+        <v>22.58</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -3808,7 +3808,7 @@
         <v>25.81</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3828,19 +3828,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>87.09999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="G4">
-        <v>12.9</v>
+        <v>6.45</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3860,19 +3860,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3892,30 +3892,30 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3984,7 +3984,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4013,81 +4013,41 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920003</v>
+        <v>20330051920060</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
         <v>68</v>
       </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920021</v>
+        <v>20330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
         <v>69</v>
       </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920060</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920035</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4124,16 +4084,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920003</v>
+        <v>20330051920060</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
         <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4141,16 +4101,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920021</v>
+        <v>20330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
         <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4158,47 +4118,47 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920060</v>
+        <v>20330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920035</v>
+        <v>20330051920361</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920002</v>
+        <v>20330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
@@ -4209,13 +4169,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920361</v>
+        <v>20330051920004</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -4226,13 +4186,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920004</v>
+        <v>20330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -4243,13 +4203,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920006</v>
+        <v>20330051920007</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -4260,13 +4220,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920007</v>
+        <v>20330051920362</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -4277,13 +4237,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920362</v>
+        <v>20330051920009</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -4294,13 +4254,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920009</v>
+        <v>20330051920011</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -4311,13 +4271,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920011</v>
+        <v>20330051920012</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4328,13 +4288,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920012</v>
+        <v>20330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -4345,13 +4305,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920013</v>
+        <v>20330051920014</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4362,13 +4322,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920014</v>
+        <v>20330051920015</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4379,13 +4339,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920015</v>
+        <v>20330051920016</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4396,13 +4356,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920016</v>
+        <v>20330051920017</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4413,13 +4373,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920017</v>
+        <v>20330051920363</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4430,13 +4390,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920363</v>
+        <v>20330051920021</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4450,10 +4410,10 @@
         <v>20330051920023</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4467,10 +4427,10 @@
         <v>20330051920025</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4484,10 +4444,10 @@
         <v>20330051920026</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4501,10 +4461,10 @@
         <v>20330051920027</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4518,10 +4478,10 @@
         <v>20330051920028</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4535,10 +4495,10 @@
         <v>20330051920029</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4552,10 +4512,10 @@
         <v>20330051920031</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4569,13 +4529,13 @@
         <v>20330051920032</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4586,10 +4546,10 @@
         <v>20330051920033</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
@@ -4603,10 +4563,10 @@
         <v>20330051920034</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -4620,13 +4580,13 @@
         <v>20330051920036</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4637,10 +4597,10 @@
         <v>20330051920037</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
@@ -4656,7 +4616,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4688,22 +4648,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920011</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4711,22 +4671,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920011</v>
+        <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4737,13 +4697,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4760,13 +4720,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4783,19 +4743,19 @@
         <v>20330051920016</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4806,19 +4766,19 @@
         <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4826,16 +4786,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920025</v>
+        <v>20330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4849,16 +4809,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920025</v>
+        <v>20330051920021</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4872,22 +4832,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920035</v>
+        <v>20330051920362</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4895,16 +4855,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920035</v>
+        <v>20330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4913,21 +4873,21 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920004</v>
+        <v>20330051920012</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4941,22 +4901,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920007</v>
+        <v>20330051920363</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4964,22 +4924,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920362</v>
+        <v>20330051920025</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4987,16 +4947,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920009</v>
+        <v>20330051920060</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -5005,21 +4965,21 @@
         <v>53</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920012</v>
+        <v>20330051920033</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -5033,185 +4993,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920014</v>
+        <v>20330051920034</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920026</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920060</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920028</v>
-      </c>
-      <c r="B20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920029</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920033</v>
-      </c>
-      <c r="B22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920034</v>
-      </c>
-      <c r="B23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920037</v>
-      </c>
-      <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20221.xlsx
+++ b/grupos/5AEM - Estadisticos 20221.xlsx
@@ -1002,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1023,7 +1023,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1180,7 +1180,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1201,7 +1201,7 @@
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1447,7 +1447,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1625,7 +1625,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1646,7 +1646,7 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1714,7 +1714,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1981,7 +1981,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -2070,7 +2070,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>10</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2248,7 +2248,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2337,7 +2337,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2426,7 +2426,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2447,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>6</v>
@@ -2515,7 +2515,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2604,7 +2604,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2693,7 +2693,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2714,7 +2714,7 @@
         <v>7</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2782,7 +2782,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2871,7 +2871,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2960,7 +2960,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2981,7 +2981,7 @@
         <v>6</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -3049,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3138,7 +3138,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3227,7 +3227,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3316,7 +3316,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3405,7 +3405,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3494,7 +3494,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3515,7 +3515,7 @@
         <v>-1</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3583,7 +3583,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3672,7 +3672,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5AEM - Estadisticos 20221.xlsx
+++ b/grupos/5AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="143">
   <si>
     <t>Materia</t>
   </si>
@@ -993,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1014,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1082,7 +1082,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1103,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1171,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1260,7 +1260,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1349,7 +1349,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1438,7 +1438,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1459,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1527,7 +1527,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1616,7 +1616,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1705,7 +1705,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1794,7 +1794,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1883,7 +1883,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1972,7 +1972,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2061,7 +2061,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2150,7 +2150,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2260,7 +2260,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2328,7 +2328,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2349,7 +2349,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2417,7 +2417,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2438,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2506,7 +2506,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2527,7 +2527,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2595,7 +2595,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2616,7 +2616,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2684,7 +2684,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2773,7 +2773,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2862,7 +2862,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2951,7 +2951,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2972,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -3040,7 +3040,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3129,7 +3129,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3218,7 +3218,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3307,7 +3307,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3396,7 +3396,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3417,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3574,7 +3574,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3663,7 +3663,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3796,19 +3796,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G3">
-        <v>25.81</v>
+        <v>9.68</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4616,7 +4616,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4648,16 +4648,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4671,16 +4671,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920002</v>
+        <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4694,22 +4694,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920013</v>
+        <v>20330051920016</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920013</v>
+        <v>20330051920016</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4740,22 +4740,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920016</v>
+        <v>20330051920002</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4763,22 +4763,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920016</v>
+        <v>20330051920362</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4786,22 +4786,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920021</v>
+        <v>20330051920011</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4809,16 +4809,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920021</v>
+        <v>20330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4832,16 +4832,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920362</v>
+        <v>20330051920021</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4855,16 +4855,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920011</v>
+        <v>20330051920060</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4873,21 +4873,21 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920012</v>
+        <v>20330051920033</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4896,121 +4896,6 @@
         <v>53</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920363</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920025</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920060</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920033</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920034</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20221.xlsx
+++ b/grupos/5AEM - Estadisticos 20221.xlsx
@@ -996,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1008,7 +1008,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1085,7 +1085,7 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1097,7 +1097,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1118,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1174,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1186,7 +1186,7 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1275,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1284,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>7</v>
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1441,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1453,7 +1453,7 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1530,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1542,7 +1542,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1563,7 +1563,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1619,7 +1619,7 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1631,7 +1631,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1652,7 +1652,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1708,7 +1708,7 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1720,7 +1720,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1741,7 +1741,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1797,7 +1797,7 @@
         <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1809,7 +1809,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1830,7 +1830,7 @@
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1886,7 +1886,7 @@
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1898,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1919,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2008,7 +2008,7 @@
         <v>9</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2064,7 +2064,7 @@
         <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2097,7 +2097,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2153,7 +2153,7 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2186,7 +2186,7 @@
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2242,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2254,7 +2254,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2275,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2331,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2343,7 +2343,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>7</v>
@@ -2364,7 +2364,7 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2420,7 +2420,7 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2432,7 +2432,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2509,7 +2509,7 @@
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2521,7 +2521,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2542,7 +2542,7 @@
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2598,7 +2598,7 @@
         <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2610,7 +2610,7 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2631,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2687,7 +2687,7 @@
         <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2699,7 +2699,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2776,7 +2776,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2788,7 +2788,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2865,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2877,7 +2877,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2898,7 +2898,7 @@
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2954,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2966,7 +2966,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -3043,7 +3043,7 @@
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -3055,7 +3055,7 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -3076,7 +3076,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3132,7 +3132,7 @@
         <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3144,7 +3144,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3233,7 +3233,7 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3254,7 +3254,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3310,7 +3310,7 @@
         <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3322,7 +3322,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3399,7 +3399,7 @@
         <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3411,7 +3411,7 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3488,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3500,7 +3500,7 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3577,7 +3577,7 @@
         <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3589,7 +3589,7 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3666,7 +3666,7 @@
         <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3678,7 +3678,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/5AEM - Estadisticos 20221.xlsx
+++ b/grupos/5AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="143">
   <si>
     <t>Materia</t>
   </si>
@@ -185,10 +185,10 @@
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
@@ -990,7 +990,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -999,7 +999,7 @@
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1011,7 +1011,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1079,7 +1079,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1100,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1109,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -1177,7 +1177,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1198,7 +1198,7 @@
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>9</v>
@@ -1257,7 +1257,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1266,7 +1266,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1346,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1355,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1435,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1444,7 +1444,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -1524,7 +1524,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1533,7 +1533,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1554,7 +1554,7 @@
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1613,7 +1613,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1622,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1702,7 +1702,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1711,7 +1711,7 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1723,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1732,7 +1732,7 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1791,7 +1791,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1880,7 +1880,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1889,7 +1889,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -2058,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>5</v>
@@ -2067,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -2079,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2147,7 +2147,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -2156,7 +2156,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2236,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2257,7 +2257,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2325,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2334,7 +2334,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2355,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2414,7 +2414,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2435,7 +2435,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2503,7 +2503,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2524,7 +2524,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2592,7 +2592,7 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2601,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2622,7 +2622,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2681,7 +2681,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>7</v>
@@ -2690,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2711,7 +2711,7 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2770,7 +2770,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>7</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>8</v>
@@ -2868,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2889,7 +2889,7 @@
         <v>9</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2948,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>6</v>
@@ -2957,7 +2957,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2978,7 +2978,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -3037,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -3046,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -3126,7 +3126,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>8</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -3215,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>8</v>
@@ -3224,7 +3224,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -3304,7 +3304,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3313,7 +3313,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3334,7 +3334,7 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3393,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -3402,7 +3402,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3423,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3482,7 +3482,7 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>5</v>
@@ -3503,7 +3503,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3571,7 +3571,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -3580,7 +3580,7 @@
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3601,7 +3601,7 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3660,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>9</v>
@@ -3669,7 +3669,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3690,7 +3690,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA34">
         <v>10</v>
@@ -3764,19 +3764,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>70.97</v>
+        <v>58.06</v>
       </c>
       <c r="G2">
-        <v>22.58</v>
+        <v>35.48</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3828,16 +3828,16 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -4616,7 +4616,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4694,22 +4694,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920016</v>
+        <v>20330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4717,25 +4717,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920016</v>
+        <v>20330051920035</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4832,22 +4832,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920021</v>
+        <v>20330051920016</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4855,16 +4855,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920060</v>
+        <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4873,21 +4873,21 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920033</v>
+        <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4896,6 +4896,121 @@
         <v>53</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920026</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920060</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920029</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920033</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920037</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20221.xlsx
+++ b/grupos/5AEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
   <si>
     <t>Materia</t>
   </si>
@@ -212,238 +212,238 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BUENO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>XOCUA</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>VINALAY</t>
   </si>
   <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ADELFO</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JESUS HAZAEL</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
     <t>ANGEL SAID</t>
   </si>
   <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
     <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>DIEGO ADELFO</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JESUS HAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
   </si>
   <si>
     <t>CRISTAL</t>
@@ -1005,7 +1005,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1094,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1183,7 +1183,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1450,7 +1450,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1539,7 +1539,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1628,7 +1628,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1717,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1806,7 +1806,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1895,7 +1895,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1916,7 +1916,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1984,7 +1984,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -2073,7 +2073,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>4</v>
@@ -2162,7 +2162,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2251,7 +2251,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2340,7 +2340,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2429,7 +2429,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2518,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2607,7 +2607,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2696,7 +2696,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2717,7 +2717,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2737,7 +2737,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>8</v>
@@ -2758,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -2779,13 +2779,13 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2800,7 +2800,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2874,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2963,7 +2963,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -3052,7 +3052,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -3141,7 +3141,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -3230,7 +3230,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3319,7 +3319,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3408,7 +3408,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3429,7 +3429,7 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3449,7 +3449,7 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>8</v>
@@ -3470,7 +3470,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -3491,13 +3491,13 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -3512,13 +3512,13 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA32">
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3586,7 +3586,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3675,7 +3675,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3767,22 +3767,22 @@
         <v>18</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>58.06</v>
       </c>
       <c r="G2">
-        <v>35.48</v>
+        <v>41.94</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3984,7 +3984,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4009,46 +4009,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920060</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920035</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4084,47 +4044,47 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920060</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920035</v>
+        <v>20330051920361</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920002</v>
+        <v>20330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
         <v>116</v>
@@ -4135,13 +4095,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920361</v>
+        <v>20330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>117</v>
@@ -4152,13 +4112,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920003</v>
+        <v>20330051920006</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
@@ -4169,13 +4129,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920004</v>
+        <v>20330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -4186,13 +4146,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920006</v>
+        <v>20330051920362</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -4203,13 +4163,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920007</v>
+        <v>20330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -4220,10 +4180,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920362</v>
+        <v>20330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>86</v>
@@ -4237,13 +4197,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920009</v>
+        <v>20330051920012</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -4254,13 +4214,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920011</v>
+        <v>20330051920013</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -4271,13 +4231,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920012</v>
+        <v>20330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4288,13 +4248,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920013</v>
+        <v>20330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -4305,13 +4265,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920014</v>
+        <v>20330051920016</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4322,13 +4282,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920015</v>
+        <v>20330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4339,13 +4299,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920016</v>
+        <v>20330051920363</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4356,13 +4316,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920017</v>
+        <v>20330051920021</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4373,13 +4333,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920363</v>
+        <v>20330051920023</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4390,13 +4350,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920021</v>
+        <v>20330051920025</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4407,13 +4367,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920023</v>
+        <v>20330051920026</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4424,13 +4384,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920025</v>
+        <v>20330051920060</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4441,13 +4401,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920026</v>
+        <v>20330051920027</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4458,13 +4418,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920027</v>
+        <v>20330051920028</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4475,13 +4435,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920028</v>
+        <v>20330051920029</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4492,13 +4452,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920029</v>
+        <v>20330051920031</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4509,16 +4469,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920031</v>
+        <v>20330051920032</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4526,16 +4486,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920032</v>
+        <v>20330051920033</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4543,13 +4503,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920033</v>
+        <v>20330051920034</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
@@ -4560,13 +4520,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920034</v>
+        <v>20330051920035</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -4580,13 +4540,13 @@
         <v>20330051920036</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4597,10 +4557,10 @@
         <v>20330051920037</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
@@ -4651,13 +4611,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4674,13 +4634,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4697,13 +4657,13 @@
         <v>20330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4720,13 +4680,13 @@
         <v>20330051920035</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4735,7 +4695,7 @@
         <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4743,13 +4703,13 @@
         <v>20330051920002</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4766,13 +4726,13 @@
         <v>20330051920362</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4789,13 +4749,13 @@
         <v>20330051920011</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4812,13 +4772,13 @@
         <v>20330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4835,13 +4795,13 @@
         <v>20330051920016</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4858,13 +4818,13 @@
         <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4881,13 +4841,13 @@
         <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4904,13 +4864,13 @@
         <v>20330051920026</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4927,13 +4887,13 @@
         <v>20330051920060</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4942,7 +4902,7 @@
         <v>53</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4950,13 +4910,13 @@
         <v>20330051920029</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4973,13 +4933,13 @@
         <v>20330051920033</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4996,10 +4956,10 @@
         <v>20330051920037</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>142</v>
